--- a/artfynd/A 17244-2022 artfynd.xlsx
+++ b/artfynd/A 17244-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17244-2022 artfynd.xlsx
+++ b/artfynd/A 17244-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101561702</v>
+        <v>101726043</v>
       </c>
       <c r="B3" t="n">
-        <v>95511</v>
+        <v>5113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,49 +820,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäck1 Sandstensmossen, Skirhult, Upl</t>
+          <t>NÖ Gumrarö , Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690483.0575409513</v>
+        <v>690488.2058470851</v>
       </c>
       <c r="R3" t="n">
-        <v>6603750.925750218</v>
+        <v>6603719.680336253</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +881,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -896,7 +891,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -910,255 +905,21 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Fridström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Fridström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>101726043</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>NÖ Gumrarö , Upl</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>690488.2058470851</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6603719.680336253</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Österåker</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Österåker</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Ronny Fors</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Ronny Fors</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>101726191</v>
-      </c>
-      <c r="B5" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lopplummer</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Vallentuna, Upl</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>690491.2458354137</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6603729.997982464</v>
-      </c>
-      <c r="S5" t="n">
-        <v>25</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Österåker</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Österåker</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2022-06-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Ronny Fors</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Ronny Fors</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17244-2022 artfynd.xlsx
+++ b/artfynd/A 17244-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101726043</v>
+        <v>101561702</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
+        <v>95511</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,44 +820,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NÖ Gumrarö , Upl</t>
+          <t>Bäck1 Sandstensmossen, Skirhult, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690488.2058470851</v>
+        <v>690483.0575409513</v>
       </c>
       <c r="R3" t="n">
-        <v>6603719.680336253</v>
+        <v>6603750.925750218</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +886,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -891,7 +896,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -905,21 +910,255 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>101726043</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5113</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NÖ Gumrarö , Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>690488.2058470851</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6603719.680336253</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-06-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-06-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Ronny Fors</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Ronny Fors</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>101726191</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95511</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lopplummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Huperzia selago</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vallentuna, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>690491.2458354137</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6603729.997982464</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
